--- a/output/Tables/2019/Monte Carlo/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_age_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>448.709</v>
+        <v>448.711</v>
       </c>
       <c r="D2">
-        <v>404.003</v>
+        <v>403.959</v>
       </c>
       <c r="E2">
-        <v>493.415</v>
+        <v>493.463</v>
       </c>
       <c r="F2">
-        <v>25651.826</v>
+        <v>25656.175</v>
       </c>
       <c r="G2">
-        <v>23131.147</v>
+        <v>23131.64</v>
       </c>
       <c r="H2">
-        <v>28172.504</v>
+        <v>28180.71</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3411692823.138</v>
+        <v>3412271255.977</v>
       </c>
       <c r="M2">
-        <v>3076442605.913</v>
+        <v>3076508146.817</v>
       </c>
       <c r="N2">
-        <v>3746943040.363</v>
+        <v>3748034365.136</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>862.073</v>
+        <v>862.605</v>
       </c>
       <c r="D3">
-        <v>785.473</v>
+        <v>786.0069999999999</v>
       </c>
       <c r="E3">
-        <v>938.672</v>
+        <v>939.204</v>
       </c>
       <c r="F3">
-        <v>40121.798</v>
+        <v>40143.862</v>
       </c>
       <c r="G3">
-        <v>36662.621</v>
+        <v>36685.18</v>
       </c>
       <c r="H3">
-        <v>43580.976</v>
+        <v>43602.544</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5336199172.141</v>
+        <v>5339133707.405</v>
       </c>
       <c r="M3">
-        <v>4876128599.84</v>
+        <v>4879128998.841</v>
       </c>
       <c r="N3">
-        <v>5796269744.442</v>
+        <v>5799138415.97</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2288.713</v>
+        <v>2288.608</v>
       </c>
       <c r="D4">
-        <v>2094.981</v>
+        <v>2095.235</v>
       </c>
       <c r="E4">
-        <v>2482.445</v>
+        <v>2481.981</v>
       </c>
       <c r="F4">
-        <v>85003.401</v>
+        <v>84982.98699999999</v>
       </c>
       <c r="G4">
-        <v>77965.022</v>
+        <v>77961.77499999999</v>
       </c>
       <c r="H4">
-        <v>92041.78</v>
+        <v>92004.198</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11305452350.948</v>
+        <v>11302737246.894</v>
       </c>
       <c r="M4">
-        <v>10369347923.614</v>
+        <v>10368916118.423</v>
       </c>
       <c r="N4">
-        <v>12241556778.281</v>
+        <v>12236558375.364</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4889.309</v>
+        <v>4887.789</v>
       </c>
       <c r="D5">
-        <v>4510.273</v>
+        <v>4508.749</v>
       </c>
       <c r="E5">
-        <v>5268.346</v>
+        <v>5266.829</v>
       </c>
       <c r="F5">
-        <v>131663.883</v>
+        <v>131611.478</v>
       </c>
       <c r="G5">
-        <v>121889.085</v>
+        <v>121840.804</v>
       </c>
       <c r="H5">
-        <v>141438.681</v>
+        <v>141382.153</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17511296474.84</v>
+        <v>17504326636.152</v>
       </c>
       <c r="M5">
-        <v>16211248322.118</v>
+        <v>16204826892.515</v>
       </c>
       <c r="N5">
-        <v>18811344627.562</v>
+        <v>18803826379.79</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10442.708</v>
+        <v>10426.116</v>
       </c>
       <c r="D6">
-        <v>9668.304</v>
+        <v>9654.466</v>
       </c>
       <c r="E6">
-        <v>11217.113</v>
+        <v>11197.766</v>
       </c>
       <c r="F6">
-        <v>178453.528</v>
+        <v>178186.292</v>
       </c>
       <c r="G6">
-        <v>165823.173</v>
+        <v>165609.925</v>
       </c>
       <c r="H6">
-        <v>191083.883</v>
+        <v>190762.659</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23734319179.561</v>
+        <v>23698776858.544</v>
       </c>
       <c r="M6">
-        <v>22054481969.219</v>
+        <v>22026120035.638</v>
       </c>
       <c r="N6">
-        <v>25414156389.903</v>
+        <v>25371433681.449</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16822.612</v>
+        <v>16758.213</v>
       </c>
       <c r="D7">
-        <v>15416.819</v>
+        <v>15371.128</v>
       </c>
       <c r="E7">
-        <v>18228.404</v>
+        <v>18145.297</v>
       </c>
       <c r="F7">
-        <v>124634.116</v>
+        <v>124278.923</v>
       </c>
       <c r="G7">
-        <v>115542.143</v>
+        <v>115240.275</v>
       </c>
       <c r="H7">
-        <v>133726.089</v>
+        <v>133317.571</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16576337436.745</v>
+        <v>16529096779.645</v>
       </c>
       <c r="M7">
-        <v>15367105011.802</v>
+        <v>15326956634.494</v>
       </c>
       <c r="N7">
-        <v>17785569861.688</v>
+        <v>17731236924.796</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>22822.408</v>
+        <v>22821.622</v>
       </c>
       <c r="D8">
-        <v>20295.704</v>
+        <v>20293.153</v>
       </c>
       <c r="E8">
-        <v>25349.113</v>
+        <v>25350.091</v>
       </c>
       <c r="F8">
-        <v>19971.573</v>
+        <v>19966.345</v>
       </c>
       <c r="G8">
-        <v>16881.277</v>
+        <v>16865.408</v>
       </c>
       <c r="H8">
-        <v>23061.869</v>
+        <v>23067.282</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2656219265.08</v>
+        <v>2655523908.926</v>
       </c>
       <c r="M8">
-        <v>2245209894.769</v>
+        <v>2243099271.695</v>
       </c>
       <c r="N8">
-        <v>3067228635.392</v>
+        <v>3067948546.157</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>228.723</v>
+        <v>230.184</v>
       </c>
       <c r="D9">
-        <v>204.201</v>
+        <v>205.183</v>
       </c>
       <c r="E9">
-        <v>253.245</v>
+        <v>255.186</v>
       </c>
       <c r="F9">
-        <v>867.22</v>
+        <v>872.77</v>
       </c>
       <c r="G9">
-        <v>773.803</v>
+        <v>777.436</v>
       </c>
       <c r="H9">
-        <v>960.638</v>
+        <v>968.103</v>
       </c>
       <c r="I9">
-        <v>12740309.425</v>
+        <v>12821735.684</v>
       </c>
       <c r="J9">
-        <v>11374391.91</v>
+        <v>11429096.188</v>
       </c>
       <c r="K9">
-        <v>14106226.941</v>
+        <v>14214375.18</v>
       </c>
       <c r="L9">
-        <v>115340277.89</v>
+        <v>116078377.386</v>
       </c>
       <c r="M9">
-        <v>102915756.433</v>
+        <v>103399048.117</v>
       </c>
       <c r="N9">
-        <v>127764799.348</v>
+        <v>128757706.655</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>480.329</v>
+        <v>479.624</v>
       </c>
       <c r="D10">
-        <v>433.438</v>
+        <v>432.97</v>
       </c>
       <c r="E10">
-        <v>527.221</v>
+        <v>526.278</v>
       </c>
       <c r="F10">
-        <v>1497.747</v>
+        <v>1499.445</v>
       </c>
       <c r="G10">
-        <v>1351.268</v>
+        <v>1353.193</v>
       </c>
       <c r="H10">
-        <v>1644.226</v>
+        <v>1645.697</v>
       </c>
       <c r="I10">
-        <v>26755312.35</v>
+        <v>26716016.693</v>
       </c>
       <c r="J10">
-        <v>24143380.802</v>
+        <v>24117296.757</v>
       </c>
       <c r="K10">
-        <v>29367243.898</v>
+        <v>29314736.628</v>
       </c>
       <c r="L10">
-        <v>199200327.186</v>
+        <v>199426190.597</v>
       </c>
       <c r="M10">
-        <v>179718611.489</v>
+        <v>179974614.406</v>
       </c>
       <c r="N10">
-        <v>218682042.883</v>
+        <v>218877766.789</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1656.05</v>
+        <v>1649.805</v>
       </c>
       <c r="D11">
-        <v>1495.146</v>
+        <v>1489.792</v>
       </c>
       <c r="E11">
-        <v>1816.953</v>
+        <v>1809.818</v>
       </c>
       <c r="F11">
-        <v>4140.537</v>
+        <v>4125.277</v>
       </c>
       <c r="G11">
-        <v>3727.558</v>
+        <v>3719.935</v>
       </c>
       <c r="H11">
-        <v>4553.517</v>
+        <v>4530.62</v>
       </c>
       <c r="I11">
-        <v>92245277.958</v>
+        <v>91897442.529</v>
       </c>
       <c r="J11">
-        <v>83282639.222</v>
+        <v>82984411.949</v>
       </c>
       <c r="K11">
-        <v>101207916.694</v>
+        <v>100810473.109</v>
       </c>
       <c r="L11">
-        <v>550691441.114</v>
+        <v>548661859.052</v>
       </c>
       <c r="M11">
-        <v>495765173.942</v>
+        <v>494751317.164</v>
       </c>
       <c r="N11">
-        <v>605617708.2869999</v>
+        <v>602572400.9400001</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3821.923</v>
+        <v>3817.78</v>
       </c>
       <c r="D12">
-        <v>3495.581</v>
+        <v>3489.935</v>
       </c>
       <c r="E12">
-        <v>4148.266</v>
+        <v>4145.625</v>
       </c>
       <c r="F12">
-        <v>6897.469</v>
+        <v>6898.723</v>
       </c>
       <c r="G12">
-        <v>6315.293</v>
+        <v>6310.331</v>
       </c>
       <c r="H12">
-        <v>7479.646</v>
+        <v>7487.116</v>
       </c>
       <c r="I12">
-        <v>212888769.485</v>
+        <v>212657986.071</v>
       </c>
       <c r="J12">
-        <v>194710831.218</v>
+        <v>194396356.065</v>
       </c>
       <c r="K12">
-        <v>231066707.753</v>
+        <v>230919616.077</v>
       </c>
       <c r="L12">
-        <v>917363402.401</v>
+        <v>917530202.971</v>
       </c>
       <c r="M12">
-        <v>839933930.585</v>
+        <v>839273995.323</v>
       </c>
       <c r="N12">
-        <v>994792874.216</v>
+        <v>995786410.618</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11549.235</v>
+        <v>11533.594</v>
       </c>
       <c r="D13">
-        <v>10611.375</v>
+        <v>10599.585</v>
       </c>
       <c r="E13">
-        <v>12487.094</v>
+        <v>12467.603</v>
       </c>
       <c r="F13">
-        <v>13733.518</v>
+        <v>13720.183</v>
       </c>
       <c r="G13">
-        <v>12597.155</v>
+        <v>12600.505</v>
       </c>
       <c r="H13">
-        <v>14869.88</v>
+        <v>14839.86</v>
       </c>
       <c r="I13">
-        <v>643315465.702</v>
+        <v>642444236.637</v>
       </c>
       <c r="J13">
-        <v>591074812.933</v>
+        <v>590418057.188</v>
       </c>
       <c r="K13">
-        <v>695556118.471</v>
+        <v>694470416.086</v>
       </c>
       <c r="L13">
-        <v>1826557832.386</v>
+        <v>1824784299.187</v>
       </c>
       <c r="M13">
-        <v>1675421582.831</v>
+        <v>1675867172.779</v>
       </c>
       <c r="N13">
-        <v>1977694081.942</v>
+        <v>1973701425.594</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13537.922</v>
+        <v>13481.094</v>
       </c>
       <c r="D14">
-        <v>12386.239</v>
+        <v>12350.631</v>
       </c>
       <c r="E14">
-        <v>14689.606</v>
+        <v>14611.558</v>
       </c>
       <c r="F14">
-        <v>8015.748</v>
+        <v>7980.642</v>
       </c>
       <c r="G14">
-        <v>7293.777</v>
+        <v>7268.045</v>
       </c>
       <c r="H14">
-        <v>8737.718999999999</v>
+        <v>8693.239</v>
       </c>
       <c r="I14">
-        <v>754089341.0140001</v>
+        <v>750923915.569</v>
       </c>
       <c r="J14">
-        <v>689938268.4400001</v>
+        <v>687954853.544</v>
       </c>
       <c r="K14">
-        <v>818240413.589</v>
+        <v>813892977.594</v>
       </c>
       <c r="L14">
-        <v>1066094450.578</v>
+        <v>1061425380.61</v>
       </c>
       <c r="M14">
-        <v>970072324.381</v>
+        <v>966650007.742</v>
       </c>
       <c r="N14">
-        <v>1162116576.774</v>
+        <v>1156200753.479</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>8918.698</v>
+        <v>8917.566999999999</v>
       </c>
       <c r="D15">
-        <v>7822.851</v>
+        <v>7836.447</v>
       </c>
       <c r="E15">
-        <v>10014.545</v>
+        <v>9998.686</v>
       </c>
       <c r="F15">
-        <v>804.617</v>
+        <v>803.347</v>
       </c>
       <c r="G15">
-        <v>650.974</v>
+        <v>652.021</v>
       </c>
       <c r="H15">
-        <v>958.26</v>
+        <v>954.672</v>
       </c>
       <c r="I15">
-        <v>496789319.087</v>
+        <v>496726304.232</v>
       </c>
       <c r="J15">
-        <v>435748454.647</v>
+        <v>436505777.593</v>
       </c>
       <c r="K15">
-        <v>557830183.527</v>
+        <v>556946830.872</v>
       </c>
       <c r="L15">
-        <v>107014049.725</v>
+        <v>106845118.255</v>
       </c>
       <c r="M15">
-        <v>86579506.082</v>
+        <v>86718837.353</v>
       </c>
       <c r="N15">
-        <v>127448593.369</v>
+        <v>126971399.158</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1924.419</v>
+        <v>1957.479</v>
       </c>
       <c r="D16">
-        <v>1593.148</v>
+        <v>1634.672</v>
       </c>
       <c r="E16">
-        <v>2255.689</v>
+        <v>2280.287</v>
       </c>
       <c r="F16">
-        <v>6479.531</v>
+        <v>6600.386</v>
       </c>
       <c r="G16">
-        <v>5300.771</v>
+        <v>5484.096</v>
       </c>
       <c r="H16">
-        <v>7658.292</v>
+        <v>7716.677</v>
       </c>
       <c r="I16">
-        <v>28494864.81</v>
+        <v>28984397.086</v>
       </c>
       <c r="J16">
-        <v>23589744.793</v>
+        <v>24204586.792</v>
       </c>
       <c r="K16">
-        <v>33399984.828</v>
+        <v>33764207.38</v>
       </c>
       <c r="L16">
-        <v>861777675.2920001</v>
+        <v>877851356.01</v>
       </c>
       <c r="M16">
-        <v>705002492.8660001</v>
+        <v>729384731.1160001</v>
       </c>
       <c r="N16">
-        <v>1018552857.717</v>
+        <v>1026317980.905</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3276.664</v>
+        <v>3313.205</v>
       </c>
       <c r="D17">
-        <v>2750.335</v>
+        <v>2799.643</v>
       </c>
       <c r="E17">
-        <v>3802.993</v>
+        <v>3826.768</v>
       </c>
       <c r="F17">
-        <v>9267.004000000001</v>
+        <v>9372.659</v>
       </c>
       <c r="G17">
-        <v>7747.117</v>
+        <v>7877.044</v>
       </c>
       <c r="H17">
-        <v>10786.891</v>
+        <v>10868.274</v>
       </c>
       <c r="I17">
-        <v>48517561.116</v>
+        <v>49058629.567</v>
       </c>
       <c r="J17">
-        <v>40724204.572</v>
+        <v>41454309.916</v>
       </c>
       <c r="K17">
-        <v>56310917.661</v>
+        <v>56662949.219</v>
       </c>
       <c r="L17">
-        <v>1232511484.527</v>
+        <v>1246563628.633</v>
       </c>
       <c r="M17">
-        <v>1030366529.56</v>
+        <v>1047646797.263</v>
       </c>
       <c r="N17">
-        <v>1434656439.495</v>
+        <v>1445480460.003</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4357.056</v>
+        <v>4367.303</v>
       </c>
       <c r="D18">
-        <v>3738.206</v>
+        <v>3751.092</v>
       </c>
       <c r="E18">
-        <v>4975.906</v>
+        <v>4983.515</v>
       </c>
       <c r="F18">
-        <v>9950.848</v>
+        <v>9950.415999999999</v>
       </c>
       <c r="G18">
-        <v>8457.313</v>
+        <v>8470.698</v>
       </c>
       <c r="H18">
-        <v>11444.383</v>
+        <v>11430.133</v>
       </c>
       <c r="I18">
-        <v>64514927.635</v>
+        <v>64666662.112</v>
       </c>
       <c r="J18">
-        <v>55351620.351</v>
+        <v>55542412.181</v>
       </c>
       <c r="K18">
-        <v>73678234.92</v>
+        <v>73790912.042</v>
       </c>
       <c r="L18">
-        <v>1323462815.864</v>
+        <v>1323405274.777</v>
       </c>
       <c r="M18">
-        <v>1124822669.01</v>
+        <v>1126602833.78</v>
       </c>
       <c r="N18">
-        <v>1522102962.718</v>
+        <v>1520207715.775</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5648.532</v>
+        <v>5679.525</v>
       </c>
       <c r="D19">
-        <v>4958.536</v>
+        <v>4996.228</v>
       </c>
       <c r="E19">
-        <v>6338.527</v>
+        <v>6362.821</v>
       </c>
       <c r="F19">
-        <v>9263.655000000001</v>
+        <v>9323.585999999999</v>
       </c>
       <c r="G19">
-        <v>8113.426</v>
+        <v>8150.694</v>
       </c>
       <c r="H19">
-        <v>10413.884</v>
+        <v>10496.478</v>
       </c>
       <c r="I19">
-        <v>83637810.884</v>
+        <v>84096722.75</v>
       </c>
       <c r="J19">
-        <v>73421047.905</v>
+        <v>73979153.807</v>
       </c>
       <c r="K19">
-        <v>93854573.86399999</v>
+        <v>94214291.692</v>
       </c>
       <c r="L19">
-        <v>1232066098.581</v>
+        <v>1240036928.114</v>
       </c>
       <c r="M19">
-        <v>1079085653.986</v>
+        <v>1084042256.99</v>
       </c>
       <c r="N19">
-        <v>1385046543.177</v>
+        <v>1396031599.238</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8198.882</v>
+        <v>8270.328</v>
       </c>
       <c r="D20">
-        <v>7374.568</v>
+        <v>7432.507</v>
       </c>
       <c r="E20">
-        <v>9023.196</v>
+        <v>9108.148999999999</v>
       </c>
       <c r="F20">
-        <v>8733.704</v>
+        <v>8802.165999999999</v>
       </c>
       <c r="G20">
-        <v>7846.823</v>
+        <v>7879.676</v>
       </c>
       <c r="H20">
-        <v>9620.585999999999</v>
+        <v>9724.656000000001</v>
       </c>
       <c r="I20">
-        <v>121400851.542</v>
+        <v>122458747.957</v>
       </c>
       <c r="J20">
-        <v>109195233.062</v>
+        <v>110053135.85</v>
       </c>
       <c r="K20">
-        <v>133606470.022</v>
+        <v>134864360.065</v>
       </c>
       <c r="L20">
-        <v>1161582685.212</v>
+        <v>1170688067.274</v>
       </c>
       <c r="M20">
-        <v>1043627495.803</v>
+        <v>1047996871.295</v>
       </c>
       <c r="N20">
-        <v>1279537874.621</v>
+        <v>1293379263.252</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5452.487</v>
+        <v>5455.999</v>
       </c>
       <c r="D21">
-        <v>4815.389</v>
+        <v>4837.638</v>
       </c>
       <c r="E21">
-        <v>6089.585</v>
+        <v>6074.359</v>
       </c>
       <c r="F21">
-        <v>2771.889</v>
+        <v>2767.141</v>
       </c>
       <c r="G21">
-        <v>2436.823</v>
+        <v>2436.877</v>
       </c>
       <c r="H21">
-        <v>3106.954</v>
+        <v>3097.405</v>
       </c>
       <c r="I21">
-        <v>80734980.06999999</v>
+        <v>80786974.97400001</v>
       </c>
       <c r="J21">
-        <v>71301470.229</v>
+        <v>71630910.977</v>
       </c>
       <c r="K21">
-        <v>90168489.911</v>
+        <v>89943038.971</v>
       </c>
       <c r="L21">
-        <v>368661199.244</v>
+        <v>368029784.364</v>
       </c>
       <c r="M21">
-        <v>324097507.57</v>
+        <v>324104652.794</v>
       </c>
       <c r="N21">
-        <v>413224890.917</v>
+        <v>411954915.933</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2147.992</v>
+        <v>2161.802</v>
       </c>
       <c r="D22">
-        <v>1792.008</v>
+        <v>1784.424</v>
       </c>
       <c r="E22">
-        <v>2503.976</v>
+        <v>2539.179</v>
       </c>
       <c r="F22">
-        <v>146.704</v>
+        <v>145.579</v>
       </c>
       <c r="G22">
-        <v>112.43</v>
+        <v>110.785</v>
       </c>
       <c r="H22">
-        <v>180.979</v>
+        <v>180.373</v>
       </c>
       <c r="I22">
-        <v>31805322.221</v>
+        <v>32009799.002</v>
       </c>
       <c r="J22">
-        <v>26534264.658</v>
+        <v>26421968.865</v>
       </c>
       <c r="K22">
-        <v>37076379.783</v>
+        <v>37597629.139</v>
       </c>
       <c r="L22">
-        <v>19511649.329</v>
+        <v>19362047.643</v>
       </c>
       <c r="M22">
-        <v>14953150.87</v>
+        <v>14734424.587</v>
       </c>
       <c r="N22">
-        <v>24070147.788</v>
+        <v>23989670.699</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>401.688</v>
+        <v>400.494</v>
       </c>
       <c r="D23">
-        <v>342.788</v>
+        <v>344.193</v>
       </c>
       <c r="E23">
-        <v>460.588</v>
+        <v>456.794</v>
       </c>
       <c r="F23">
-        <v>1617.923</v>
+        <v>1617.151</v>
       </c>
       <c r="G23">
-        <v>1372.989</v>
+        <v>1387.229</v>
       </c>
       <c r="H23">
-        <v>1862.857</v>
+        <v>1847.073</v>
       </c>
       <c r="I23">
-        <v>30207355.135</v>
+        <v>30117524.011</v>
       </c>
       <c r="J23">
-        <v>25778025.057</v>
+        <v>25883675.707</v>
       </c>
       <c r="K23">
-        <v>34636685.213</v>
+        <v>34351372.315</v>
       </c>
       <c r="L23">
-        <v>215183726.403</v>
+        <v>215081096.449</v>
       </c>
       <c r="M23">
-        <v>182607501.824</v>
+        <v>184501464.572</v>
       </c>
       <c r="N23">
-        <v>247759950.983</v>
+        <v>245660728.326</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>648.242</v>
+        <v>651.222</v>
       </c>
       <c r="D24">
-        <v>564.686</v>
+        <v>565.7619999999999</v>
       </c>
       <c r="E24">
-        <v>731.797</v>
+        <v>736.682</v>
       </c>
       <c r="F24">
-        <v>2157.528</v>
+        <v>2169.98</v>
       </c>
       <c r="G24">
-        <v>1873.873</v>
+        <v>1882.36</v>
       </c>
       <c r="H24">
-        <v>2441.183</v>
+        <v>2457.6</v>
       </c>
       <c r="I24">
-        <v>48748410.007</v>
+        <v>48972554.629</v>
       </c>
       <c r="J24">
-        <v>42464930.798</v>
+        <v>42545849.093</v>
       </c>
       <c r="K24">
-        <v>55031889.216</v>
+        <v>55399260.166</v>
       </c>
       <c r="L24">
-        <v>286951198.763</v>
+        <v>288607370.31</v>
       </c>
       <c r="M24">
-        <v>249225053.358</v>
+        <v>250353897.614</v>
       </c>
       <c r="N24">
-        <v>324677344.169</v>
+        <v>326860843.006</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>969.538</v>
+        <v>958.236</v>
       </c>
       <c r="D25">
-        <v>837.337</v>
+        <v>834.66</v>
       </c>
       <c r="E25">
-        <v>1101.739</v>
+        <v>1081.812</v>
       </c>
       <c r="F25">
-        <v>2555.908</v>
+        <v>2540.511</v>
       </c>
       <c r="G25">
-        <v>2207.364</v>
+        <v>2206.099</v>
       </c>
       <c r="H25">
-        <v>2904.452</v>
+        <v>2874.923</v>
       </c>
       <c r="I25">
-        <v>72910232.979</v>
+        <v>72060308.322</v>
       </c>
       <c r="J25">
-        <v>62968615.093</v>
+        <v>62767242.496</v>
       </c>
       <c r="K25">
-        <v>82851850.86399999</v>
+        <v>81353374.148</v>
       </c>
       <c r="L25">
-        <v>339935759.488</v>
+        <v>337887922.979</v>
       </c>
       <c r="M25">
-        <v>293579368.165</v>
+        <v>293411144.82</v>
       </c>
       <c r="N25">
-        <v>386292150.81</v>
+        <v>382364701.139</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1510.019</v>
+        <v>1514.678</v>
       </c>
       <c r="D26">
-        <v>1347.744</v>
+        <v>1346.665</v>
       </c>
       <c r="E26">
-        <v>1672.294</v>
+        <v>1682.692</v>
       </c>
       <c r="F26">
-        <v>2924.061</v>
+        <v>2932.161</v>
       </c>
       <c r="G26">
-        <v>2595.231</v>
+        <v>2604.262</v>
       </c>
       <c r="H26">
-        <v>3252.892</v>
+        <v>3260.06</v>
       </c>
       <c r="I26">
-        <v>113554941.946</v>
+        <v>113905330.034</v>
       </c>
       <c r="J26">
-        <v>101351707.115</v>
+        <v>101270575.841</v>
       </c>
       <c r="K26">
-        <v>125758176.777</v>
+        <v>126540084.226</v>
       </c>
       <c r="L26">
-        <v>388900132.322</v>
+        <v>389977405.089</v>
       </c>
       <c r="M26">
-        <v>345165690.115</v>
+        <v>346366790.382</v>
       </c>
       <c r="N26">
-        <v>432634574.529</v>
+        <v>433588019.797</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2143.836</v>
+        <v>2159.063</v>
       </c>
       <c r="D27">
-        <v>1913.505</v>
+        <v>1939.855</v>
       </c>
       <c r="E27">
-        <v>2374.168</v>
+        <v>2378.271</v>
       </c>
       <c r="F27">
-        <v>2780.435</v>
+        <v>2794.784</v>
       </c>
       <c r="G27">
-        <v>2480.775</v>
+        <v>2505</v>
       </c>
       <c r="H27">
-        <v>3080.096</v>
+        <v>3084.568</v>
       </c>
       <c r="I27">
-        <v>161218645.595</v>
+        <v>162363720.356</v>
       </c>
       <c r="J27">
-        <v>143897473.813</v>
+        <v>145879059.572</v>
       </c>
       <c r="K27">
-        <v>178539817.377</v>
+        <v>178848381.14</v>
       </c>
       <c r="L27">
-        <v>369797916.937</v>
+        <v>371706293.035</v>
       </c>
       <c r="M27">
-        <v>329943013.207</v>
+        <v>333164987.174</v>
       </c>
       <c r="N27">
-        <v>409652820.666</v>
+        <v>410247598.897</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>694.961</v>
+        <v>692.182</v>
       </c>
       <c r="D28">
-        <v>617.529</v>
+        <v>616.028</v>
       </c>
       <c r="E28">
-        <v>772.393</v>
+        <v>768.336</v>
       </c>
       <c r="F28">
-        <v>458.801</v>
+        <v>457.069</v>
       </c>
       <c r="G28">
-        <v>403.617</v>
+        <v>401.703</v>
       </c>
       <c r="H28">
-        <v>513.985</v>
+        <v>512.4349999999999</v>
       </c>
       <c r="I28">
-        <v>52261753.354</v>
+        <v>52052767.696</v>
       </c>
       <c r="J28">
-        <v>46438783.931</v>
+        <v>46325903.821</v>
       </c>
       <c r="K28">
-        <v>58084722.776</v>
+        <v>57779631.572</v>
       </c>
       <c r="L28">
-        <v>61020497.951</v>
+        <v>60790145.968</v>
       </c>
       <c r="M28">
-        <v>53681008.89</v>
+        <v>53426435.689</v>
       </c>
       <c r="N28">
-        <v>68359987.01100001</v>
+        <v>68153856.24600001</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>27.912</v>
+        <v>28.022</v>
       </c>
       <c r="D29">
-        <v>23.48</v>
+        <v>23.437</v>
       </c>
       <c r="E29">
-        <v>32.344</v>
+        <v>32.607</v>
       </c>
       <c r="F29">
-        <v>3.18</v>
+        <v>3.154</v>
       </c>
       <c r="G29">
-        <v>2.347</v>
+        <v>2.364</v>
       </c>
       <c r="H29">
-        <v>4.014</v>
+        <v>3.944</v>
       </c>
       <c r="I29">
-        <v>2099037.968</v>
+        <v>2107249.258</v>
       </c>
       <c r="J29">
-        <v>1765742.3</v>
+        <v>1762452.199</v>
       </c>
       <c r="K29">
-        <v>2432333.635</v>
+        <v>2452046.317</v>
       </c>
       <c r="L29">
-        <v>423000.144</v>
+        <v>419441.022</v>
       </c>
       <c r="M29">
-        <v>312086.237</v>
+        <v>314367.143</v>
       </c>
       <c r="N29">
-        <v>533914.051</v>
+        <v>524514.9</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>162.668</v>
+        <v>162.697</v>
       </c>
       <c r="D32">
-        <v>146.873</v>
+        <v>147.033</v>
       </c>
       <c r="E32">
-        <v>178.463</v>
+        <v>178.36</v>
       </c>
       <c r="F32">
-        <v>1328.389</v>
+        <v>1324.956</v>
       </c>
       <c r="G32">
-        <v>1192.895</v>
+        <v>1192.637</v>
       </c>
       <c r="H32">
-        <v>1463.883</v>
+        <v>1457.274</v>
       </c>
       <c r="I32">
-        <v>2739166.303</v>
+        <v>2739651.458</v>
       </c>
       <c r="J32">
-        <v>2473200.093</v>
+        <v>2475895.992</v>
       </c>
       <c r="K32">
-        <v>3005132.514</v>
+        <v>3003406.925</v>
       </c>
       <c r="L32">
-        <v>176675743.054</v>
+        <v>176219113.24</v>
       </c>
       <c r="M32">
-        <v>158655096.474</v>
+        <v>158620743.791</v>
       </c>
       <c r="N32">
-        <v>194696389.635</v>
+        <v>193817482.688</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>319.432</v>
+        <v>321.573</v>
       </c>
       <c r="D33">
-        <v>292.291</v>
+        <v>293.713</v>
       </c>
       <c r="E33">
-        <v>346.574</v>
+        <v>349.433</v>
       </c>
       <c r="F33">
-        <v>1904.343</v>
+        <v>1912.968</v>
       </c>
       <c r="G33">
-        <v>1739.432</v>
+        <v>1742.701</v>
       </c>
       <c r="H33">
-        <v>2069.253</v>
+        <v>2083.235</v>
       </c>
       <c r="I33">
-        <v>5378919.087</v>
+        <v>5414962.996</v>
       </c>
       <c r="J33">
-        <v>4921884.902</v>
+        <v>4945826.681</v>
       </c>
       <c r="K33">
-        <v>5835953.273</v>
+        <v>5884099.312</v>
       </c>
       <c r="L33">
-        <v>253277556.382</v>
+        <v>254424745.765</v>
       </c>
       <c r="M33">
-        <v>231344466.629</v>
+        <v>231779280.122</v>
       </c>
       <c r="N33">
-        <v>275210646.134</v>
+        <v>277070211.409</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1884.99</v>
+        <v>1881.597</v>
       </c>
       <c r="D34">
-        <v>1745.561</v>
+        <v>1740.846</v>
       </c>
       <c r="E34">
-        <v>2024.42</v>
+        <v>2022.348</v>
       </c>
       <c r="F34">
-        <v>7437.37</v>
+        <v>7429.153</v>
       </c>
       <c r="G34">
-        <v>6858.741</v>
+        <v>6851.021</v>
       </c>
       <c r="H34">
-        <v>8015.999</v>
+        <v>8007.285</v>
       </c>
       <c r="I34">
-        <v>31741349.362</v>
+        <v>31684213.207</v>
       </c>
       <c r="J34">
-        <v>29393497.082</v>
+        <v>29314104.575</v>
       </c>
       <c r="K34">
-        <v>34089201.643</v>
+        <v>34054321.84</v>
       </c>
       <c r="L34">
-        <v>989170213.198</v>
+        <v>988077355.478</v>
       </c>
       <c r="M34">
-        <v>912212600.181</v>
+        <v>911185811.609</v>
       </c>
       <c r="N34">
-        <v>1066127826.215</v>
+        <v>1064968899.347</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5154.115</v>
+        <v>5146.199</v>
       </c>
       <c r="D35">
-        <v>4725.937</v>
+        <v>4726.893</v>
       </c>
       <c r="E35">
-        <v>5582.294</v>
+        <v>5565.506</v>
       </c>
       <c r="F35">
-        <v>10450.143</v>
+        <v>10441.955</v>
       </c>
       <c r="G35">
-        <v>9487.849</v>
+        <v>9484.440000000001</v>
       </c>
       <c r="H35">
-        <v>11412.437</v>
+        <v>11399.47</v>
       </c>
       <c r="I35">
-        <v>86790150.17900001</v>
+        <v>86656852.56200001</v>
       </c>
       <c r="J35">
-        <v>79580049.07700001</v>
+        <v>79596146.98899999</v>
       </c>
       <c r="K35">
-        <v>94000251.28</v>
+        <v>93717558.13600001</v>
       </c>
       <c r="L35">
-        <v>1389869065.059</v>
+        <v>1388779972.369</v>
       </c>
       <c r="M35">
-        <v>1261883978.191</v>
+        <v>1261430490.527</v>
       </c>
       <c r="N35">
-        <v>1517854151.927</v>
+        <v>1516129454.21</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6452.158</v>
+        <v>6423.882</v>
       </c>
       <c r="D36">
-        <v>5685.535</v>
+        <v>5674.621</v>
       </c>
       <c r="E36">
-        <v>7218.781</v>
+        <v>7173.143</v>
       </c>
       <c r="F36">
-        <v>2135.891</v>
+        <v>2132.98</v>
       </c>
       <c r="G36">
-        <v>1732.979</v>
+        <v>1737.208</v>
       </c>
       <c r="H36">
-        <v>2538.802</v>
+        <v>2528.753</v>
       </c>
       <c r="I36">
-        <v>108647888.126</v>
+        <v>108171753.167</v>
       </c>
       <c r="J36">
-        <v>95738718.367</v>
+        <v>95554948.176</v>
       </c>
       <c r="K36">
-        <v>121557057.885</v>
+        <v>120788558.158</v>
       </c>
       <c r="L36">
-        <v>284073462.861</v>
+        <v>283686390.93</v>
       </c>
       <c r="M36">
-        <v>230486204.488</v>
+        <v>231048603.127</v>
       </c>
       <c r="N36">
-        <v>337660721.234</v>
+        <v>336324178.733</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>23586.491</v>
+        <v>23500.928</v>
       </c>
       <c r="D37">
-        <v>20742.835</v>
+        <v>20709.235</v>
       </c>
       <c r="E37">
-        <v>26430.147</v>
+        <v>26292.62</v>
       </c>
       <c r="F37">
-        <v>123341.508</v>
+        <v>2780.533</v>
       </c>
       <c r="G37">
-        <v>107475.081</v>
+        <v>2432.42</v>
       </c>
       <c r="H37">
-        <v>139207.935</v>
+        <v>3128.646</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>16404420564.016</v>
+        <v>369810851.568</v>
       </c>
       <c r="M37">
-        <v>14294185831.901</v>
+        <v>323511838.847</v>
       </c>
       <c r="N37">
-        <v>18514655296.13</v>
+        <v>416109864.289</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>25332.057</v>
+        <v>25298.228</v>
       </c>
       <c r="D38">
-        <v>22533.166</v>
+        <v>22490.119</v>
       </c>
       <c r="E38">
-        <v>28130.949</v>
+        <v>28106.337</v>
       </c>
       <c r="F38">
-        <v>109696.563</v>
+        <v>2992.09</v>
       </c>
       <c r="G38">
-        <v>96657.65700000001</v>
+        <v>2642.36</v>
       </c>
       <c r="H38">
-        <v>122735.468</v>
+        <v>3341.821</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>14589642821.086</v>
+        <v>397948012.793</v>
       </c>
       <c r="M38">
-        <v>12855468441.732</v>
+        <v>351433820.827</v>
       </c>
       <c r="N38">
-        <v>16323817200.441</v>
+        <v>444462204.758</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>23989.546</v>
+        <v>24011.028</v>
       </c>
       <c r="D39">
-        <v>21505.828</v>
+        <v>21507.328</v>
       </c>
       <c r="E39">
-        <v>26473.264</v>
+        <v>26514.728</v>
       </c>
       <c r="F39">
-        <v>84245.617</v>
+        <v>2840.258</v>
       </c>
       <c r="G39">
-        <v>74447.28999999999</v>
+        <v>2528.103</v>
       </c>
       <c r="H39">
-        <v>94043.944</v>
+        <v>3152.412</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>11204667008.177</v>
+        <v>377754269.971</v>
       </c>
       <c r="M39">
-        <v>9901489514.638</v>
+        <v>336237705.852</v>
       </c>
       <c r="N39">
-        <v>12507844501.717</v>
+        <v>419270834.09</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>23427.121</v>
+        <v>23356.728</v>
       </c>
       <c r="D40">
-        <v>21165.937</v>
+        <v>21129.325</v>
       </c>
       <c r="E40">
-        <v>25688.305</v>
+        <v>25584.13</v>
       </c>
       <c r="F40">
-        <v>60144.738</v>
+        <v>2762.844</v>
       </c>
       <c r="G40">
-        <v>53872.435</v>
+        <v>2485.624</v>
       </c>
       <c r="H40">
-        <v>66417.042</v>
+        <v>3040.064</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>7999250191.77</v>
+        <v>367458315.097</v>
       </c>
       <c r="M40">
-        <v>7165033804.996</v>
+        <v>330588057.148</v>
       </c>
       <c r="N40">
-        <v>8833466578.545</v>
+        <v>404328573.047</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>28321.878</v>
+        <v>28412.842</v>
       </c>
       <c r="D41">
-        <v>26035.391</v>
+        <v>26114.864</v>
       </c>
       <c r="E41">
-        <v>30608.364</v>
+        <v>30710.82</v>
       </c>
       <c r="F41">
-        <v>49017.247</v>
+        <v>3360.373</v>
       </c>
       <c r="G41">
-        <v>44499.693</v>
+        <v>3073.96</v>
       </c>
       <c r="H41">
-        <v>53534.801</v>
+        <v>3646.786</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>6519293867.102</v>
+        <v>446929653.609</v>
       </c>
       <c r="M41">
-        <v>5918459213.001</v>
+        <v>408836716.42</v>
       </c>
       <c r="N41">
-        <v>7120128521.204</v>
+        <v>485022590.798</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>19091.347</v>
+        <v>19085.418</v>
       </c>
       <c r="D42">
-        <v>17374.505</v>
+        <v>17355.103</v>
       </c>
       <c r="E42">
-        <v>20808.189</v>
+        <v>20815.732</v>
       </c>
       <c r="F42">
-        <v>17638.898</v>
+        <v>2250.313</v>
       </c>
       <c r="G42">
-        <v>15718.406</v>
+        <v>2035.174</v>
       </c>
       <c r="H42">
-        <v>19559.39</v>
+        <v>2465.452</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>2345973464.716</v>
+        <v>299291585.128</v>
       </c>
       <c r="M42">
-        <v>2090548003.193</v>
+        <v>270678086.27</v>
       </c>
       <c r="N42">
-        <v>2601398926.24</v>
+        <v>327905083.986</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>8256.598</v>
+        <v>8263.281999999999</v>
       </c>
       <c r="D43">
-        <v>7198.959</v>
+        <v>7209.04</v>
       </c>
       <c r="E43">
-        <v>9314.236000000001</v>
+        <v>9317.525</v>
       </c>
       <c r="F43">
-        <v>1339.168</v>
+        <v>524.753</v>
       </c>
       <c r="G43">
-        <v>1062.297</v>
+        <v>427.649</v>
       </c>
       <c r="H43">
-        <v>1616.038</v>
+        <v>621.857</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>178109304.923</v>
+        <v>69792149.267</v>
       </c>
       <c r="M43">
-        <v>141285517.53</v>
+        <v>56877309.697</v>
       </c>
       <c r="N43">
-        <v>214933092.315</v>
+        <v>82706988.838</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Monte Carlo/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_age_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>448.711</v>
+        <v>448.857</v>
       </c>
       <c r="D2">
-        <v>403.959</v>
+        <v>404.061</v>
       </c>
       <c r="E2">
-        <v>493.463</v>
+        <v>493.654</v>
       </c>
       <c r="F2">
-        <v>25656.175</v>
+        <v>25664.448</v>
       </c>
       <c r="G2">
-        <v>23131.64</v>
+        <v>23137.392</v>
       </c>
       <c r="H2">
-        <v>28180.71</v>
+        <v>28191.504</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3412271255.977</v>
+        <v>3413371636.644</v>
       </c>
       <c r="M2">
-        <v>3076508146.817</v>
+        <v>3077273177.779</v>
       </c>
       <c r="N2">
-        <v>3748034365.136</v>
+        <v>3749470095.508</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>862.605</v>
+        <v>862.232</v>
       </c>
       <c r="D3">
-        <v>786.0069999999999</v>
+        <v>785.706</v>
       </c>
       <c r="E3">
-        <v>939.204</v>
+        <v>938.758</v>
       </c>
       <c r="F3">
-        <v>40143.862</v>
+        <v>40127.098</v>
       </c>
       <c r="G3">
-        <v>36685.18</v>
+        <v>36671.604</v>
       </c>
       <c r="H3">
-        <v>43602.544</v>
+        <v>43582.593</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5339133707.405</v>
+        <v>5336904064.02</v>
       </c>
       <c r="M3">
-        <v>4879128998.841</v>
+        <v>4877323265.686</v>
       </c>
       <c r="N3">
-        <v>5799138415.97</v>
+        <v>5796484862.354</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2288.608</v>
+        <v>2289.38</v>
       </c>
       <c r="D4">
-        <v>2095.235</v>
+        <v>2095.817</v>
       </c>
       <c r="E4">
-        <v>2481.981</v>
+        <v>2482.943</v>
       </c>
       <c r="F4">
-        <v>84982.98699999999</v>
+        <v>85010.749</v>
       </c>
       <c r="G4">
-        <v>77961.77499999999</v>
+        <v>77982.94500000001</v>
       </c>
       <c r="H4">
-        <v>92004.198</v>
+        <v>92038.554</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11302737246.894</v>
+        <v>11306429677.133</v>
       </c>
       <c r="M4">
-        <v>10368916118.423</v>
+        <v>10371731654.105</v>
       </c>
       <c r="N4">
-        <v>12236558375.364</v>
+        <v>12241127700.161</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4887.789</v>
+        <v>4888.423</v>
       </c>
       <c r="D5">
-        <v>4508.749</v>
+        <v>4509.489</v>
       </c>
       <c r="E5">
-        <v>5266.829</v>
+        <v>5267.358</v>
       </c>
       <c r="F5">
-        <v>131611.478</v>
+        <v>131628.436</v>
       </c>
       <c r="G5">
-        <v>121840.804</v>
+        <v>121860.417</v>
       </c>
       <c r="H5">
-        <v>141382.153</v>
+        <v>141396.455</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17504326636.152</v>
+        <v>17506581964.512</v>
       </c>
       <c r="M5">
-        <v>16204826892.515</v>
+        <v>16207435416.793</v>
       </c>
       <c r="N5">
-        <v>18803826379.79</v>
+        <v>18805728512.23</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10426.116</v>
+        <v>10426.338</v>
       </c>
       <c r="D6">
-        <v>9654.466</v>
+        <v>9654.411</v>
       </c>
       <c r="E6">
-        <v>11197.766</v>
+        <v>11198.266</v>
       </c>
       <c r="F6">
-        <v>178186.292</v>
+        <v>178192.619</v>
       </c>
       <c r="G6">
-        <v>165609.925</v>
+        <v>165610.393</v>
       </c>
       <c r="H6">
-        <v>190762.659</v>
+        <v>190774.845</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23698776858.544</v>
+        <v>23699618325.084</v>
       </c>
       <c r="M6">
-        <v>22026120035.638</v>
+        <v>22026182224.281</v>
       </c>
       <c r="N6">
-        <v>25371433681.449</v>
+        <v>25373054425.887</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16758.213</v>
+        <v>16759.41</v>
       </c>
       <c r="D7">
-        <v>15371.128</v>
+        <v>15372.803</v>
       </c>
       <c r="E7">
-        <v>18145.297</v>
+        <v>18146.016</v>
       </c>
       <c r="F7">
-        <v>124278.923</v>
+        <v>124294.685</v>
       </c>
       <c r="G7">
-        <v>115240.275</v>
+        <v>115253.862</v>
       </c>
       <c r="H7">
-        <v>133317.571</v>
+        <v>133335.508</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16529096779.645</v>
+        <v>16531193115.848</v>
       </c>
       <c r="M7">
-        <v>15326956634.494</v>
+        <v>15328763694.42</v>
       </c>
       <c r="N7">
-        <v>17731236924.796</v>
+        <v>17733622537.276</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>22821.622</v>
+        <v>22824.043</v>
       </c>
       <c r="D8">
-        <v>20293.153</v>
+        <v>20295.324</v>
       </c>
       <c r="E8">
-        <v>25350.091</v>
+        <v>25352.761</v>
       </c>
       <c r="F8">
-        <v>19966.345</v>
+        <v>19972.496</v>
       </c>
       <c r="G8">
-        <v>16865.408</v>
+        <v>16870.185</v>
       </c>
       <c r="H8">
-        <v>23067.282</v>
+        <v>23074.807</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2655523908.926</v>
+        <v>2656341973.283</v>
       </c>
       <c r="M8">
-        <v>2243099271.695</v>
+        <v>2243734630.471</v>
       </c>
       <c r="N8">
-        <v>3067948546.157</v>
+        <v>3068949316.095</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>230.184</v>
+        <v>231.497</v>
       </c>
       <c r="D9">
-        <v>205.183</v>
+        <v>206.325</v>
       </c>
       <c r="E9">
-        <v>255.186</v>
+        <v>256.67</v>
       </c>
       <c r="F9">
-        <v>872.77</v>
+        <v>877.853</v>
       </c>
       <c r="G9">
-        <v>777.436</v>
+        <v>781.835</v>
       </c>
       <c r="H9">
-        <v>968.103</v>
+        <v>973.87</v>
       </c>
       <c r="I9">
-        <v>12821735.684</v>
+        <v>12894872.445</v>
       </c>
       <c r="J9">
-        <v>11429096.188</v>
+        <v>11492730.942</v>
       </c>
       <c r="K9">
-        <v>14214375.18</v>
+        <v>14297013.947</v>
       </c>
       <c r="L9">
-        <v>116078377.386</v>
+        <v>116754390.141</v>
       </c>
       <c r="M9">
-        <v>103399048.117</v>
+        <v>103984058.216</v>
       </c>
       <c r="N9">
-        <v>128757706.655</v>
+        <v>129524722.067</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>479.624</v>
+        <v>481.237</v>
       </c>
       <c r="D10">
-        <v>432.97</v>
+        <v>434.345</v>
       </c>
       <c r="E10">
-        <v>526.278</v>
+        <v>528.129</v>
       </c>
       <c r="F10">
-        <v>1499.445</v>
+        <v>1504.136</v>
       </c>
       <c r="G10">
-        <v>1353.193</v>
+        <v>1357.352</v>
       </c>
       <c r="H10">
-        <v>1645.697</v>
+        <v>1650.92</v>
       </c>
       <c r="I10">
-        <v>26716016.693</v>
+        <v>26805858.867</v>
       </c>
       <c r="J10">
-        <v>24117296.757</v>
+        <v>24193876.893</v>
       </c>
       <c r="K10">
-        <v>29314736.628</v>
+        <v>29417840.841</v>
       </c>
       <c r="L10">
-        <v>199426190.597</v>
+        <v>200050066.378</v>
       </c>
       <c r="M10">
-        <v>179974614.406</v>
+        <v>180527838.816</v>
       </c>
       <c r="N10">
-        <v>218877766.789</v>
+        <v>219572293.939</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1649.805</v>
+        <v>1648.333</v>
       </c>
       <c r="D11">
-        <v>1489.792</v>
+        <v>1488.037</v>
       </c>
       <c r="E11">
-        <v>1809.818</v>
+        <v>1808.629</v>
       </c>
       <c r="F11">
-        <v>4125.277</v>
+        <v>4121.652</v>
       </c>
       <c r="G11">
-        <v>3719.935</v>
+        <v>3714.986</v>
       </c>
       <c r="H11">
-        <v>4530.62</v>
+        <v>4528.317</v>
       </c>
       <c r="I11">
-        <v>91897442.529</v>
+        <v>91815461.36</v>
       </c>
       <c r="J11">
-        <v>82984411.949</v>
+        <v>82886649.63699999</v>
       </c>
       <c r="K11">
-        <v>100810473.109</v>
+        <v>100744273.083</v>
       </c>
       <c r="L11">
-        <v>548661859.052</v>
+        <v>548179662.375</v>
       </c>
       <c r="M11">
-        <v>494751317.164</v>
+        <v>494093101.95</v>
       </c>
       <c r="N11">
-        <v>602572400.9400001</v>
+        <v>602266222.799</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3817.78</v>
+        <v>3824.068</v>
       </c>
       <c r="D12">
-        <v>3489.935</v>
+        <v>3495.531</v>
       </c>
       <c r="E12">
-        <v>4145.625</v>
+        <v>4152.604</v>
       </c>
       <c r="F12">
-        <v>6898.723</v>
+        <v>6910.842</v>
       </c>
       <c r="G12">
-        <v>6310.331</v>
+        <v>6321.071</v>
       </c>
       <c r="H12">
-        <v>7487.116</v>
+        <v>7500.612</v>
       </c>
       <c r="I12">
-        <v>212657986.071</v>
+        <v>213008214.593</v>
       </c>
       <c r="J12">
-        <v>194396356.065</v>
+        <v>194708060.158</v>
       </c>
       <c r="K12">
-        <v>230919616.077</v>
+        <v>231308369.027</v>
       </c>
       <c r="L12">
-        <v>917530202.971</v>
+        <v>919141935.568</v>
       </c>
       <c r="M12">
-        <v>839273995.323</v>
+        <v>840702416.056</v>
       </c>
       <c r="N12">
-        <v>995786410.618</v>
+        <v>997581455.08</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11533.594</v>
+        <v>11571.624</v>
       </c>
       <c r="D13">
-        <v>10599.585</v>
+        <v>10632.911</v>
       </c>
       <c r="E13">
-        <v>12467.603</v>
+        <v>12510.337</v>
       </c>
       <c r="F13">
-        <v>13720.183</v>
+        <v>13758.267</v>
       </c>
       <c r="G13">
-        <v>12600.505</v>
+        <v>12635.602</v>
       </c>
       <c r="H13">
-        <v>14839.86</v>
+        <v>14880.931</v>
       </c>
       <c r="I13">
-        <v>642444236.637</v>
+        <v>644562591.0420001</v>
       </c>
       <c r="J13">
-        <v>590418057.188</v>
+        <v>592274385.443</v>
       </c>
       <c r="K13">
-        <v>694470416.086</v>
+        <v>696850796.64</v>
       </c>
       <c r="L13">
-        <v>1824784299.187</v>
+        <v>1829849469.729</v>
       </c>
       <c r="M13">
-        <v>1675867172.779</v>
+        <v>1680535069.765</v>
       </c>
       <c r="N13">
-        <v>1973701425.594</v>
+        <v>1979163869.693</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13481.094</v>
+        <v>13476.493</v>
       </c>
       <c r="D14">
-        <v>12350.631</v>
+        <v>12346.944</v>
       </c>
       <c r="E14">
-        <v>14611.558</v>
+        <v>14606.043</v>
       </c>
       <c r="F14">
-        <v>7980.642</v>
+        <v>7965.927</v>
       </c>
       <c r="G14">
-        <v>7268.045</v>
+        <v>7255.466</v>
       </c>
       <c r="H14">
-        <v>8693.239</v>
+        <v>8676.388000000001</v>
       </c>
       <c r="I14">
-        <v>750923915.569</v>
+        <v>750667622.188</v>
       </c>
       <c r="J14">
-        <v>687954853.544</v>
+        <v>687749448.295</v>
       </c>
       <c r="K14">
-        <v>813892977.594</v>
+        <v>813585796.082</v>
       </c>
       <c r="L14">
-        <v>1061425380.61</v>
+        <v>1059468287.269</v>
       </c>
       <c r="M14">
-        <v>966650007.742</v>
+        <v>964976981.6799999</v>
       </c>
       <c r="N14">
-        <v>1156200753.479</v>
+        <v>1153959592.858</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>8917.566999999999</v>
+        <v>8920.395</v>
       </c>
       <c r="D15">
-        <v>7836.447</v>
+        <v>7836.114</v>
       </c>
       <c r="E15">
-        <v>9998.686</v>
+        <v>10004.676</v>
       </c>
       <c r="F15">
-        <v>803.347</v>
+        <v>800.289</v>
       </c>
       <c r="G15">
-        <v>652.021</v>
+        <v>649.433</v>
       </c>
       <c r="H15">
-        <v>954.672</v>
+        <v>951.145</v>
       </c>
       <c r="I15">
-        <v>496726304.232</v>
+        <v>496883839.295</v>
       </c>
       <c r="J15">
-        <v>436505777.593</v>
+        <v>436487228.615</v>
       </c>
       <c r="K15">
-        <v>556946830.872</v>
+        <v>557280449.975</v>
       </c>
       <c r="L15">
-        <v>106845118.255</v>
+        <v>106438473.999</v>
       </c>
       <c r="M15">
-        <v>86718837.353</v>
+        <v>86374637.06999999</v>
       </c>
       <c r="N15">
-        <v>126971399.158</v>
+        <v>126502310.929</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1957.479</v>
+        <v>1956.365</v>
       </c>
       <c r="D16">
-        <v>1634.672</v>
+        <v>1631.443</v>
       </c>
       <c r="E16">
-        <v>2280.287</v>
+        <v>2281.287</v>
       </c>
       <c r="F16">
-        <v>6600.386</v>
+        <v>6598.776</v>
       </c>
       <c r="G16">
-        <v>5484.096</v>
+        <v>5473.424</v>
       </c>
       <c r="H16">
-        <v>7716.677</v>
+        <v>7724.127</v>
       </c>
       <c r="I16">
-        <v>28984397.086</v>
+        <v>28967895.9</v>
       </c>
       <c r="J16">
-        <v>24204586.792</v>
+        <v>24156776.957</v>
       </c>
       <c r="K16">
-        <v>33764207.38</v>
+        <v>33779014.842</v>
       </c>
       <c r="L16">
-        <v>877851356.01</v>
+        <v>877637153.942</v>
       </c>
       <c r="M16">
-        <v>729384731.1160001</v>
+        <v>727965382.169</v>
       </c>
       <c r="N16">
-        <v>1026317980.905</v>
+        <v>1027308925.715</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3313.205</v>
+        <v>3344.961</v>
       </c>
       <c r="D17">
-        <v>2799.643</v>
+        <v>2824.49</v>
       </c>
       <c r="E17">
-        <v>3826.768</v>
+        <v>3865.432</v>
       </c>
       <c r="F17">
-        <v>9372.659</v>
+        <v>9468.994000000001</v>
       </c>
       <c r="G17">
-        <v>7877.044</v>
+        <v>7956.093</v>
       </c>
       <c r="H17">
-        <v>10868.274</v>
+        <v>10981.896</v>
       </c>
       <c r="I17">
-        <v>49058629.567</v>
+        <v>49528835.39</v>
       </c>
       <c r="J17">
-        <v>41454309.916</v>
+        <v>41822221.612</v>
       </c>
       <c r="K17">
-        <v>56662949.219</v>
+        <v>57235449.168</v>
       </c>
       <c r="L17">
-        <v>1246563628.633</v>
+        <v>1259376263.648</v>
       </c>
       <c r="M17">
-        <v>1047646797.263</v>
+        <v>1058160318.905</v>
       </c>
       <c r="N17">
-        <v>1445480460.003</v>
+        <v>1460592208.391</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4367.303</v>
+        <v>4376.991</v>
       </c>
       <c r="D18">
-        <v>3751.092</v>
+        <v>3758.446</v>
       </c>
       <c r="E18">
-        <v>4983.515</v>
+        <v>4995.537</v>
       </c>
       <c r="F18">
-        <v>9950.415999999999</v>
+        <v>9969.606</v>
       </c>
       <c r="G18">
-        <v>8470.698</v>
+        <v>8485.638999999999</v>
       </c>
       <c r="H18">
-        <v>11430.133</v>
+        <v>11453.572</v>
       </c>
       <c r="I18">
-        <v>64666662.112</v>
+        <v>64810112.811</v>
       </c>
       <c r="J18">
-        <v>55542412.181</v>
+        <v>55651304.202</v>
       </c>
       <c r="K18">
-        <v>73790912.042</v>
+        <v>73968921.419</v>
       </c>
       <c r="L18">
-        <v>1323405274.777</v>
+        <v>1325957573.164</v>
       </c>
       <c r="M18">
-        <v>1126602833.78</v>
+        <v>1128590032.129</v>
       </c>
       <c r="N18">
-        <v>1520207715.775</v>
+        <v>1523325114.199</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5679.525</v>
+        <v>5694.146</v>
       </c>
       <c r="D19">
-        <v>4996.228</v>
+        <v>5010.677</v>
       </c>
       <c r="E19">
-        <v>6362.821</v>
+        <v>6377.616</v>
       </c>
       <c r="F19">
-        <v>9323.585999999999</v>
+        <v>9344.888999999999</v>
       </c>
       <c r="G19">
-        <v>8150.694</v>
+        <v>8175.225</v>
       </c>
       <c r="H19">
-        <v>10496.478</v>
+        <v>10514.553</v>
       </c>
       <c r="I19">
-        <v>84096722.75</v>
+        <v>84313225.148</v>
       </c>
       <c r="J19">
-        <v>73979153.807</v>
+        <v>74193090.84999999</v>
       </c>
       <c r="K19">
-        <v>94214291.692</v>
+        <v>94433359.44499999</v>
       </c>
       <c r="L19">
-        <v>1240036928.114</v>
+        <v>1242870234.178</v>
       </c>
       <c r="M19">
-        <v>1084042256.99</v>
+        <v>1087304981.331</v>
       </c>
       <c r="N19">
-        <v>1396031599.238</v>
+        <v>1398435487.025</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8270.328</v>
+        <v>8237.906999999999</v>
       </c>
       <c r="D20">
-        <v>7432.507</v>
+        <v>7396.088</v>
       </c>
       <c r="E20">
-        <v>9108.148999999999</v>
+        <v>9079.727000000001</v>
       </c>
       <c r="F20">
-        <v>8802.165999999999</v>
+        <v>8766.402</v>
       </c>
       <c r="G20">
-        <v>7879.676</v>
+        <v>7841.835</v>
       </c>
       <c r="H20">
-        <v>9724.656000000001</v>
+        <v>9690.969999999999</v>
       </c>
       <c r="I20">
-        <v>122458747.957</v>
+        <v>121978694.253</v>
       </c>
       <c r="J20">
-        <v>110053135.85</v>
+        <v>109513877.119</v>
       </c>
       <c r="K20">
-        <v>134864360.065</v>
+        <v>134443511.388</v>
       </c>
       <c r="L20">
-        <v>1170688067.274</v>
+        <v>1165931490.962</v>
       </c>
       <c r="M20">
-        <v>1047996871.295</v>
+        <v>1042964012.479</v>
       </c>
       <c r="N20">
-        <v>1293379263.252</v>
+        <v>1288898969.445</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5455.999</v>
+        <v>5443.025</v>
       </c>
       <c r="D21">
-        <v>4837.638</v>
+        <v>4824.552</v>
       </c>
       <c r="E21">
-        <v>6074.359</v>
+        <v>6061.498</v>
       </c>
       <c r="F21">
-        <v>2767.141</v>
+        <v>2759.39</v>
       </c>
       <c r="G21">
-        <v>2436.877</v>
+        <v>2428.202</v>
       </c>
       <c r="H21">
-        <v>3097.405</v>
+        <v>3090.578</v>
       </c>
       <c r="I21">
-        <v>80786974.97400001</v>
+        <v>80594868.279</v>
       </c>
       <c r="J21">
-        <v>71630910.977</v>
+        <v>71437135.88</v>
       </c>
       <c r="K21">
-        <v>89943038.971</v>
+        <v>89752600.678</v>
       </c>
       <c r="L21">
-        <v>368029784.364</v>
+        <v>366998838.964</v>
       </c>
       <c r="M21">
-        <v>324104652.794</v>
+        <v>322950805.303</v>
       </c>
       <c r="N21">
-        <v>411954915.933</v>
+        <v>411046872.625</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2161.802</v>
+        <v>2159.334</v>
       </c>
       <c r="D22">
-        <v>1784.424</v>
+        <v>1780.812</v>
       </c>
       <c r="E22">
-        <v>2539.179</v>
+        <v>2537.857</v>
       </c>
       <c r="F22">
-        <v>145.579</v>
+        <v>144.702</v>
       </c>
       <c r="G22">
-        <v>110.785</v>
+        <v>110.104</v>
       </c>
       <c r="H22">
-        <v>180.373</v>
+        <v>179.3</v>
       </c>
       <c r="I22">
-        <v>32009799.002</v>
+        <v>31973264.929</v>
       </c>
       <c r="J22">
-        <v>26421968.865</v>
+        <v>26368487.656</v>
       </c>
       <c r="K22">
-        <v>37597629.139</v>
+        <v>37578042.203</v>
       </c>
       <c r="L22">
-        <v>19362047.643</v>
+        <v>19245382.89</v>
       </c>
       <c r="M22">
-        <v>14734424.587</v>
+        <v>14643805.581</v>
       </c>
       <c r="N22">
-        <v>23989670.699</v>
+        <v>23846960.2</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>400.494</v>
+        <v>402.67</v>
       </c>
       <c r="D23">
-        <v>344.193</v>
+        <v>346.313</v>
       </c>
       <c r="E23">
-        <v>456.794</v>
+        <v>459.026</v>
       </c>
       <c r="F23">
-        <v>1617.151</v>
+        <v>1625.2</v>
       </c>
       <c r="G23">
-        <v>1387.229</v>
+        <v>1394.729</v>
       </c>
       <c r="H23">
-        <v>1847.073</v>
+        <v>1855.67</v>
       </c>
       <c r="I23">
-        <v>30117524.011</v>
+        <v>30281167.866</v>
       </c>
       <c r="J23">
-        <v>25883675.707</v>
+        <v>26043084.613</v>
       </c>
       <c r="K23">
-        <v>34351372.315</v>
+        <v>34519251.118</v>
       </c>
       <c r="L23">
-        <v>215081096.449</v>
+        <v>216151538.287</v>
       </c>
       <c r="M23">
-        <v>184501464.572</v>
+        <v>185499018.544</v>
       </c>
       <c r="N23">
-        <v>245660728.326</v>
+        <v>246804058.029</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>651.222</v>
+        <v>645.063</v>
       </c>
       <c r="D24">
-        <v>565.7619999999999</v>
+        <v>560.08</v>
       </c>
       <c r="E24">
-        <v>736.682</v>
+        <v>730.047</v>
       </c>
       <c r="F24">
-        <v>2169.98</v>
+        <v>2147.34</v>
       </c>
       <c r="G24">
-        <v>1882.36</v>
+        <v>1861.745</v>
       </c>
       <c r="H24">
-        <v>2457.6</v>
+        <v>2432.934</v>
       </c>
       <c r="I24">
-        <v>48972554.629</v>
+        <v>48509415.258</v>
       </c>
       <c r="J24">
-        <v>42545849.093</v>
+        <v>42118586.733</v>
       </c>
       <c r="K24">
-        <v>55399260.166</v>
+        <v>54900243.783</v>
       </c>
       <c r="L24">
-        <v>288607370.31</v>
+        <v>285596176.371</v>
       </c>
       <c r="M24">
-        <v>250353897.614</v>
+        <v>247612133.925</v>
       </c>
       <c r="N24">
-        <v>326860843.006</v>
+        <v>323580218.816</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>958.236</v>
+        <v>956.91</v>
       </c>
       <c r="D25">
-        <v>834.66</v>
+        <v>833.918</v>
       </c>
       <c r="E25">
-        <v>1081.812</v>
+        <v>1079.903</v>
       </c>
       <c r="F25">
-        <v>2540.511</v>
+        <v>2536.546</v>
       </c>
       <c r="G25">
-        <v>2206.099</v>
+        <v>2204.484</v>
       </c>
       <c r="H25">
-        <v>2874.923</v>
+        <v>2868.607</v>
       </c>
       <c r="I25">
-        <v>72060308.322</v>
+        <v>71960611.73</v>
       </c>
       <c r="J25">
-        <v>62767242.496</v>
+        <v>62711448.656</v>
       </c>
       <c r="K25">
-        <v>81353374.148</v>
+        <v>81209774.80400001</v>
       </c>
       <c r="L25">
-        <v>337887922.979</v>
+        <v>337360564.343</v>
       </c>
       <c r="M25">
-        <v>293411144.82</v>
+        <v>293196368.534</v>
       </c>
       <c r="N25">
-        <v>382364701.139</v>
+        <v>381524760.153</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1514.678</v>
+        <v>1515.731</v>
       </c>
       <c r="D26">
-        <v>1346.665</v>
+        <v>1346.652</v>
       </c>
       <c r="E26">
-        <v>1682.692</v>
+        <v>1684.809</v>
       </c>
       <c r="F26">
-        <v>2932.161</v>
+        <v>2933.855</v>
       </c>
       <c r="G26">
-        <v>2604.262</v>
+        <v>2603.312</v>
       </c>
       <c r="H26">
-        <v>3260.06</v>
+        <v>3264.397</v>
       </c>
       <c r="I26">
-        <v>113905330.034</v>
+        <v>113984453.53</v>
       </c>
       <c r="J26">
-        <v>101270575.841</v>
+        <v>101269559.258</v>
       </c>
       <c r="K26">
-        <v>126540084.226</v>
+        <v>126699347.801</v>
       </c>
       <c r="L26">
-        <v>389977405.089</v>
+        <v>390202666.857</v>
       </c>
       <c r="M26">
-        <v>346366790.382</v>
+        <v>346240469.36</v>
       </c>
       <c r="N26">
-        <v>433588019.797</v>
+        <v>434164864.354</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2159.063</v>
+        <v>2163.509</v>
       </c>
       <c r="D27">
-        <v>1939.855</v>
+        <v>1943.636</v>
       </c>
       <c r="E27">
-        <v>2378.271</v>
+        <v>2383.381</v>
       </c>
       <c r="F27">
-        <v>2794.784</v>
+        <v>2803.173</v>
       </c>
       <c r="G27">
-        <v>2505</v>
+        <v>2512.016</v>
       </c>
       <c r="H27">
-        <v>3084.568</v>
+        <v>3094.329</v>
       </c>
       <c r="I27">
-        <v>162363720.356</v>
+        <v>162698016.164</v>
       </c>
       <c r="J27">
-        <v>145879059.572</v>
+        <v>146163400.835</v>
       </c>
       <c r="K27">
-        <v>178848381.14</v>
+        <v>179232631.493</v>
       </c>
       <c r="L27">
-        <v>371706293.035</v>
+        <v>372821947.698</v>
       </c>
       <c r="M27">
-        <v>333164987.174</v>
+        <v>334098113.291</v>
       </c>
       <c r="N27">
-        <v>410247598.897</v>
+        <v>411545782.104</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>692.182</v>
+        <v>696.381</v>
       </c>
       <c r="D28">
-        <v>616.028</v>
+        <v>619.347</v>
       </c>
       <c r="E28">
-        <v>768.336</v>
+        <v>773.414</v>
       </c>
       <c r="F28">
-        <v>457.069</v>
+        <v>460.532</v>
       </c>
       <c r="G28">
-        <v>401.703</v>
+        <v>404.1</v>
       </c>
       <c r="H28">
-        <v>512.4349999999999</v>
+        <v>516.9640000000001</v>
       </c>
       <c r="I28">
-        <v>52052767.696</v>
+        <v>52368519.929</v>
       </c>
       <c r="J28">
-        <v>46325903.821</v>
+        <v>46575537.956</v>
       </c>
       <c r="K28">
-        <v>57779631.572</v>
+        <v>58161501.901</v>
       </c>
       <c r="L28">
-        <v>60790145.968</v>
+        <v>61250793.067</v>
       </c>
       <c r="M28">
-        <v>53426435.689</v>
+        <v>53745317.174</v>
       </c>
       <c r="N28">
-        <v>68153856.24600001</v>
+        <v>68756268.961</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>28.022</v>
+        <v>27.762</v>
       </c>
       <c r="D29">
-        <v>23.437</v>
+        <v>23.201</v>
       </c>
       <c r="E29">
-        <v>32.607</v>
+        <v>32.323</v>
       </c>
       <c r="F29">
-        <v>3.154</v>
+        <v>3.121</v>
       </c>
       <c r="G29">
-        <v>2.364</v>
+        <v>2.335</v>
       </c>
       <c r="H29">
-        <v>3.944</v>
+        <v>3.907</v>
       </c>
       <c r="I29">
-        <v>2107249.258</v>
+        <v>2087730.509</v>
       </c>
       <c r="J29">
-        <v>1762452.199</v>
+        <v>1744729.276</v>
       </c>
       <c r="K29">
-        <v>2452046.317</v>
+        <v>2430731.742</v>
       </c>
       <c r="L29">
-        <v>419441.022</v>
+        <v>415100.532</v>
       </c>
       <c r="M29">
-        <v>314367.143</v>
+        <v>310554.461</v>
       </c>
       <c r="N29">
-        <v>524514.9</v>
+        <v>519646.604</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>162.697</v>
+        <v>164.793</v>
       </c>
       <c r="D32">
-        <v>147.033</v>
+        <v>148.951</v>
       </c>
       <c r="E32">
-        <v>178.36</v>
+        <v>180.634</v>
       </c>
       <c r="F32">
-        <v>1324.956</v>
+        <v>1341.668</v>
       </c>
       <c r="G32">
-        <v>1192.637</v>
+        <v>1208.009</v>
       </c>
       <c r="H32">
-        <v>1457.274</v>
+        <v>1475.326</v>
       </c>
       <c r="I32">
-        <v>2739651.458</v>
+        <v>2774942.564</v>
       </c>
       <c r="J32">
-        <v>2475895.992</v>
+        <v>2508180.947</v>
       </c>
       <c r="K32">
-        <v>3003406.925</v>
+        <v>3041704.181</v>
       </c>
       <c r="L32">
-        <v>176219113.24</v>
+        <v>178441798.194</v>
       </c>
       <c r="M32">
-        <v>158620743.791</v>
+        <v>160665251.876</v>
       </c>
       <c r="N32">
-        <v>193817482.688</v>
+        <v>196218344.512</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>321.573</v>
+        <v>316.368</v>
       </c>
       <c r="D33">
-        <v>293.713</v>
+        <v>288.994</v>
       </c>
       <c r="E33">
-        <v>349.433</v>
+        <v>343.742</v>
       </c>
       <c r="F33">
-        <v>1912.968</v>
+        <v>1880.012</v>
       </c>
       <c r="G33">
-        <v>1742.701</v>
+        <v>1712.903</v>
       </c>
       <c r="H33">
-        <v>2083.235</v>
+        <v>2047.121</v>
       </c>
       <c r="I33">
-        <v>5414962.996</v>
+        <v>5327318.468</v>
       </c>
       <c r="J33">
-        <v>4945826.681</v>
+        <v>4866362.569</v>
       </c>
       <c r="K33">
-        <v>5884099.312</v>
+        <v>5788274.368</v>
       </c>
       <c r="L33">
-        <v>254424745.765</v>
+        <v>250041604.212</v>
       </c>
       <c r="M33">
-        <v>231779280.122</v>
+        <v>227816066.925</v>
       </c>
       <c r="N33">
-        <v>277070211.409</v>
+        <v>272267141.5</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1881.597</v>
+        <v>1892.446</v>
       </c>
       <c r="D34">
-        <v>1740.846</v>
+        <v>1751.092</v>
       </c>
       <c r="E34">
-        <v>2022.348</v>
+        <v>2033.8</v>
       </c>
       <c r="F34">
-        <v>7429.153</v>
+        <v>7475.846</v>
       </c>
       <c r="G34">
-        <v>6851.021</v>
+        <v>6895.713</v>
       </c>
       <c r="H34">
-        <v>8007.285</v>
+        <v>8055.979</v>
       </c>
       <c r="I34">
-        <v>31684213.207</v>
+        <v>31866896.777</v>
       </c>
       <c r="J34">
-        <v>29314104.575</v>
+        <v>29486631.33</v>
       </c>
       <c r="K34">
-        <v>34054321.84</v>
+        <v>34247162.225</v>
       </c>
       <c r="L34">
-        <v>988077355.478</v>
+        <v>994287540.8559999</v>
       </c>
       <c r="M34">
-        <v>911185811.609</v>
+        <v>917129851.142</v>
       </c>
       <c r="N34">
-        <v>1064968899.347</v>
+        <v>1071445230.569</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5146.199</v>
+        <v>5140.312</v>
       </c>
       <c r="D35">
-        <v>4726.893</v>
+        <v>4721.506</v>
       </c>
       <c r="E35">
-        <v>5565.506</v>
+        <v>5559.117</v>
       </c>
       <c r="F35">
-        <v>10441.955</v>
+        <v>10420.447</v>
       </c>
       <c r="G35">
-        <v>9484.440000000001</v>
+        <v>9464.362999999999</v>
       </c>
       <c r="H35">
-        <v>11399.47</v>
+        <v>11376.532</v>
       </c>
       <c r="I35">
-        <v>86656852.56200001</v>
+        <v>86557708.49600001</v>
       </c>
       <c r="J35">
-        <v>79596146.98899999</v>
+        <v>79505447.352</v>
       </c>
       <c r="K35">
-        <v>93717558.13600001</v>
+        <v>93609969.641</v>
       </c>
       <c r="L35">
-        <v>1388779972.369</v>
+        <v>1385919499.617</v>
       </c>
       <c r="M35">
-        <v>1261430490.527</v>
+        <v>1258760234.384</v>
       </c>
       <c r="N35">
-        <v>1516129454.21</v>
+        <v>1513078764.849</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6423.882</v>
+        <v>6417.715</v>
       </c>
       <c r="D36">
-        <v>5674.621</v>
+        <v>5668.849</v>
       </c>
       <c r="E36">
-        <v>7173.143</v>
+        <v>7166.581</v>
       </c>
       <c r="F36">
-        <v>2132.98</v>
+        <v>2135.295</v>
       </c>
       <c r="G36">
-        <v>1737.208</v>
+        <v>1739.816</v>
       </c>
       <c r="H36">
-        <v>2528.753</v>
+        <v>2530.774</v>
       </c>
       <c r="I36">
-        <v>108171753.167</v>
+        <v>108067906.007</v>
       </c>
       <c r="J36">
-        <v>95554948.176</v>
+        <v>95457747.28300001</v>
       </c>
       <c r="K36">
-        <v>120788558.158</v>
+        <v>120678064.732</v>
       </c>
       <c r="L36">
-        <v>283686390.93</v>
+        <v>283994227.076</v>
       </c>
       <c r="M36">
-        <v>231048603.127</v>
+        <v>231395532.494</v>
       </c>
       <c r="N36">
-        <v>336324178.733</v>
+        <v>336592921.659</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>23500.928</v>
+        <v>19059.373</v>
       </c>
       <c r="D37">
-        <v>20709.235</v>
+        <v>16678.194</v>
       </c>
       <c r="E37">
-        <v>26292.62</v>
+        <v>21440.553</v>
       </c>
       <c r="F37">
-        <v>2780.533</v>
+        <v>10754.246</v>
       </c>
       <c r="G37">
-        <v>2432.42</v>
+        <v>9323.852999999999</v>
       </c>
       <c r="H37">
-        <v>3128.646</v>
+        <v>12184.638</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>369810851.568</v>
+        <v>1430314694.148</v>
       </c>
       <c r="M37">
-        <v>323511838.847</v>
+        <v>1240072476.212</v>
       </c>
       <c r="N37">
-        <v>416109864.289</v>
+        <v>1620556912.083</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>25298.228</v>
+        <v>20627.366</v>
       </c>
       <c r="D38">
-        <v>22490.119</v>
+        <v>18217.853</v>
       </c>
       <c r="E38">
-        <v>28106.337</v>
+        <v>23036.879</v>
       </c>
       <c r="F38">
-        <v>2992.09</v>
+        <v>9857.593000000001</v>
       </c>
       <c r="G38">
-        <v>2642.36</v>
+        <v>8627.902</v>
       </c>
       <c r="H38">
-        <v>3341.821</v>
+        <v>11087.284</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>397948012.793</v>
+        <v>1311059824.67</v>
       </c>
       <c r="M38">
-        <v>351433820.827</v>
+        <v>1147510922.221</v>
       </c>
       <c r="N38">
-        <v>444462204.758</v>
+        <v>1474608727.12</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>24011.028</v>
+        <v>19804.174</v>
       </c>
       <c r="D39">
-        <v>21507.328</v>
+        <v>17650.574</v>
       </c>
       <c r="E39">
-        <v>26514.728</v>
+        <v>21957.774</v>
       </c>
       <c r="F39">
-        <v>2840.258</v>
+        <v>7833.167</v>
       </c>
       <c r="G39">
-        <v>2528.103</v>
+        <v>6899.255</v>
       </c>
       <c r="H39">
-        <v>3152.412</v>
+        <v>8767.079</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>377754269.971</v>
+        <v>1041811263.848</v>
       </c>
       <c r="M39">
-        <v>336237705.852</v>
+        <v>917600968.066</v>
       </c>
       <c r="N39">
-        <v>419270834.09</v>
+        <v>1166021559.629</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>23356.728</v>
+        <v>19532.838</v>
       </c>
       <c r="D40">
-        <v>21129.325</v>
+        <v>17606.472</v>
       </c>
       <c r="E40">
-        <v>25584.13</v>
+        <v>21459.204</v>
       </c>
       <c r="F40">
-        <v>2762.844</v>
+        <v>5819.533</v>
       </c>
       <c r="G40">
-        <v>2485.624</v>
+        <v>5192.584</v>
       </c>
       <c r="H40">
-        <v>3040.064</v>
+        <v>6446.483</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>367458315.097</v>
+        <v>773997952.4220001</v>
       </c>
       <c r="M40">
-        <v>330588057.148</v>
+        <v>690613645.9400001</v>
       </c>
       <c r="N40">
-        <v>404328573.047</v>
+        <v>857382258.904</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>28412.842</v>
+        <v>23814.422</v>
       </c>
       <c r="D41">
-        <v>26114.864</v>
+        <v>21819.172</v>
       </c>
       <c r="E41">
-        <v>30710.82</v>
+        <v>25809.672</v>
       </c>
       <c r="F41">
-        <v>3360.373</v>
+        <v>4863.278</v>
       </c>
       <c r="G41">
-        <v>3073.96</v>
+        <v>4410.115</v>
       </c>
       <c r="H41">
-        <v>3646.786</v>
+        <v>5316.441</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>446929653.609</v>
+        <v>646816011.408</v>
       </c>
       <c r="M41">
-        <v>408836716.42</v>
+        <v>586545361.197</v>
       </c>
       <c r="N41">
-        <v>485022590.798</v>
+        <v>707086661.62</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>19085.418</v>
+        <v>16054.343</v>
       </c>
       <c r="D42">
-        <v>17355.103</v>
+        <v>14552.917</v>
       </c>
       <c r="E42">
-        <v>20815.732</v>
+        <v>17555.77</v>
       </c>
       <c r="F42">
-        <v>2250.313</v>
+        <v>1769.424</v>
       </c>
       <c r="G42">
-        <v>2035.174</v>
+        <v>1569.03</v>
       </c>
       <c r="H42">
-        <v>2465.452</v>
+        <v>1969.818</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>299291585.128</v>
+        <v>235333355.395</v>
       </c>
       <c r="M42">
-        <v>270678086.27</v>
+        <v>208680950.991</v>
       </c>
       <c r="N42">
-        <v>327905083.986</v>
+        <v>261985759.8</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>8263.281999999999</v>
+        <v>7116.33</v>
       </c>
       <c r="D43">
-        <v>7209.04</v>
+        <v>6183.013</v>
       </c>
       <c r="E43">
-        <v>9317.525</v>
+        <v>8049.646</v>
       </c>
       <c r="F43">
-        <v>524.753</v>
+        <v>144.073</v>
       </c>
       <c r="G43">
-        <v>427.649</v>
+        <v>114.073</v>
       </c>
       <c r="H43">
-        <v>621.857</v>
+        <v>174.073</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>69792149.267</v>
+        <v>19161736.984</v>
       </c>
       <c r="M43">
-        <v>56877309.697</v>
+        <v>15171771.786</v>
       </c>
       <c r="N43">
-        <v>82706988.838</v>
+        <v>23151702.182</v>
       </c>
     </row>
   </sheetData>
